--- a/data/review/gpt-5.4-pro/step-4-review-reviewed.xlsx
+++ b/data/review/gpt-5.4-pro/step-4-review-reviewed.xlsx
@@ -8,19 +8,19 @@
     <sheet state="visible" name="removed" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">review!$A$1:$Y$160</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">review!$A$1:$Y$161</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="razsmn3okKRfcCpxFMAmnRz0ibK6DAbX00TAd47/7R4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="AzdEz/S3FLsJ++uVsafQEEMZILDSGh01BxQox40YWBY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3102" uniqueCount="2512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3117" uniqueCount="2516">
   <si>
     <t>ID</t>
   </si>
@@ -13065,6 +13065,18 @@
   <si>
     <t>type: primary study
 note: The paper presents a primary study that proposes, implements, and evaluates the SuperCoder technique.</t>
+  </si>
+  <si>
+    <t>HF40</t>
+  </si>
+  <si>
+    <t>CodeFusion: A Pre-trained Diffusion Model for Code Generation</t>
+  </si>
+  <si>
+    <t>This paper has been withdrawn by Mukul Singh</t>
+  </si>
+  <si>
+    <t>not available</t>
   </si>
   <si>
     <t>HF41</t>
@@ -19445,10 +19457,10 @@
         <v>863</v>
       </c>
       <c r="O61" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P61" s="14" t="s">
         <v>89</v>
-      </c>
-      <c r="P61" s="14" t="s">
-        <v>32</v>
       </c>
       <c r="Q61" s="24" t="s">
         <v>89</v>
@@ -25071,57 +25083,53 @@
       <c r="Y151" s="25"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="5" t="s">
+      <c r="A152" s="40" t="s">
         <v>2149</v>
       </c>
-      <c r="B152" s="6" t="s">
+      <c r="B152" s="23" t="s">
         <v>2150</v>
       </c>
-      <c r="C152" s="6" t="s">
+      <c r="C152" s="6"/>
+      <c r="D152" s="22"/>
+      <c r="E152" s="23" t="s">
         <v>2151</v>
       </c>
-      <c r="D152" s="7" t="s">
+      <c r="F152" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="G152" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="H152" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I152" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="J152" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="K152" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="L152" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="M152" s="23" t="s">
         <v>2152</v>
       </c>
-      <c r="E152" s="23" t="s">
-        <v>2153</v>
-      </c>
-      <c r="F152" s="23" t="s">
-        <v>2154</v>
-      </c>
-      <c r="G152" s="23" t="s">
-        <v>2155</v>
-      </c>
-      <c r="H152" s="23" t="s">
-        <v>2156</v>
-      </c>
-      <c r="I152" s="23" t="s">
-        <v>2157</v>
-      </c>
-      <c r="J152" s="23" t="s">
-        <v>2158</v>
-      </c>
-      <c r="K152" s="23" t="s">
-        <v>2159</v>
-      </c>
-      <c r="L152" s="23" t="s">
-        <v>2160</v>
-      </c>
-      <c r="M152" s="6" t="s">
-        <v>2161</v>
-      </c>
-      <c r="N152" s="6" t="s">
-        <v>2162</v>
+      <c r="N152" s="23" t="s">
+        <v>2151</v>
       </c>
       <c r="O152" s="9" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="P152" s="9" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="Q152" s="10"/>
       <c r="R152" s="9" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="S152" s="5"/>
       <c r="T152" s="5"/>
@@ -25132,508 +25140,569 @@
       <c r="Y152" s="5"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="11" t="s">
+      <c r="A153" s="5" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="E153" s="23" t="s">
+        <v>2157</v>
+      </c>
+      <c r="F153" s="23" t="s">
+        <v>2158</v>
+      </c>
+      <c r="G153" s="23" t="s">
+        <v>2159</v>
+      </c>
+      <c r="H153" s="23" t="s">
+        <v>2160</v>
+      </c>
+      <c r="I153" s="23" t="s">
+        <v>2161</v>
+      </c>
+      <c r="J153" s="23" t="s">
+        <v>2162</v>
+      </c>
+      <c r="K153" s="23" t="s">
         <v>2163</v>
       </c>
-      <c r="B153" s="12" t="s">
+      <c r="L153" s="23" t="s">
         <v>2164</v>
       </c>
-      <c r="C153" s="12" t="s">
+      <c r="M153" s="6" t="s">
         <v>2165</v>
       </c>
-      <c r="D153" s="13" t="s">
+      <c r="N153" s="6" t="s">
         <v>2166</v>
       </c>
-      <c r="E153" s="12" t="s">
-        <v>2167</v>
-      </c>
-      <c r="F153" s="12" t="s">
-        <v>2168</v>
-      </c>
-      <c r="G153" s="12" t="s">
-        <v>2169</v>
-      </c>
-      <c r="H153" s="12" t="s">
-        <v>2170</v>
-      </c>
-      <c r="I153" s="12" t="s">
-        <v>2171</v>
-      </c>
-      <c r="J153" s="12" t="s">
-        <v>2172</v>
-      </c>
-      <c r="K153" s="12" t="s">
-        <v>2173</v>
-      </c>
-      <c r="L153" s="12" t="s">
-        <v>2174</v>
-      </c>
-      <c r="M153" s="12" t="s">
-        <v>2175</v>
-      </c>
-      <c r="N153" s="12" t="s">
-        <v>2176</v>
-      </c>
-      <c r="O153" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P153" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q153" s="15"/>
-      <c r="R153" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="S153" s="32" t="s">
-        <v>2177</v>
-      </c>
-      <c r="T153" s="11"/>
-      <c r="U153" s="11"/>
-      <c r="V153" s="11"/>
-      <c r="W153" s="11"/>
-      <c r="X153" s="11"/>
-      <c r="Y153" s="11"/>
+      <c r="O153" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P153" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q153" s="10"/>
+      <c r="R153" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S153" s="5"/>
+      <c r="T153" s="5"/>
+      <c r="U153" s="5"/>
+      <c r="V153" s="5"/>
+      <c r="W153" s="5"/>
+      <c r="X153" s="5"/>
+      <c r="Y153" s="5"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="25" t="s">
+      <c r="A154" s="11" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D154" s="13" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E154" s="12" t="s">
+        <v>2171</v>
+      </c>
+      <c r="F154" s="12" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G154" s="12" t="s">
+        <v>2173</v>
+      </c>
+      <c r="H154" s="12" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I154" s="12" t="s">
+        <v>2175</v>
+      </c>
+      <c r="J154" s="12" t="s">
+        <v>2176</v>
+      </c>
+      <c r="K154" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="L154" s="12" t="s">
         <v>2178</v>
       </c>
-      <c r="B154" s="26" t="s">
+      <c r="M154" s="12" t="s">
         <v>2179</v>
       </c>
-      <c r="C154" s="26" t="s">
+      <c r="N154" s="12" t="s">
         <v>2180</v>
       </c>
-      <c r="D154" s="27" t="s">
+      <c r="O154" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P154" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q154" s="15"/>
+      <c r="R154" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="S154" s="32" t="s">
         <v>2181</v>
       </c>
-      <c r="E154" s="26" t="s">
-        <v>2182</v>
-      </c>
-      <c r="F154" s="26" t="s">
-        <v>2183</v>
-      </c>
-      <c r="G154" s="26" t="s">
-        <v>2184</v>
-      </c>
-      <c r="H154" s="26" t="s">
-        <v>2185</v>
-      </c>
-      <c r="I154" s="26" t="s">
-        <v>2186</v>
-      </c>
-      <c r="J154" s="26" t="s">
-        <v>2187</v>
-      </c>
-      <c r="K154" s="26" t="s">
-        <v>2188</v>
-      </c>
-      <c r="L154" s="26" t="s">
-        <v>2189</v>
-      </c>
-      <c r="M154" s="26" t="s">
-        <v>2190</v>
-      </c>
-      <c r="N154" s="26" t="s">
-        <v>2191</v>
-      </c>
-      <c r="O154" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="P154" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q154" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="R154" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="S154" s="25"/>
-      <c r="T154" s="25"/>
-      <c r="U154" s="25"/>
-      <c r="V154" s="25"/>
-      <c r="W154" s="25"/>
-      <c r="X154" s="25"/>
-      <c r="Y154" s="25"/>
+      <c r="T154" s="11"/>
+      <c r="U154" s="11"/>
+      <c r="V154" s="11"/>
+      <c r="W154" s="11"/>
+      <c r="X154" s="11"/>
+      <c r="Y154" s="11"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="5" t="s">
+      <c r="A155" s="25" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B155" s="26" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C155" s="26" t="s">
+        <v>2184</v>
+      </c>
+      <c r="D155" s="27" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E155" s="26" t="s">
+        <v>2186</v>
+      </c>
+      <c r="F155" s="26" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G155" s="26" t="s">
+        <v>2188</v>
+      </c>
+      <c r="H155" s="26" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I155" s="26" t="s">
+        <v>2190</v>
+      </c>
+      <c r="J155" s="26" t="s">
+        <v>2191</v>
+      </c>
+      <c r="K155" s="26" t="s">
         <v>2192</v>
       </c>
-      <c r="B155" s="6" t="s">
+      <c r="L155" s="26" t="s">
         <v>2193</v>
       </c>
-      <c r="C155" s="6" t="s">
+      <c r="M155" s="26" t="s">
         <v>2194</v>
       </c>
-      <c r="D155" s="7" t="s">
+      <c r="N155" s="26" t="s">
         <v>2195</v>
       </c>
-      <c r="E155" s="23" t="s">
-        <v>2196</v>
-      </c>
-      <c r="F155" s="23" t="s">
-        <v>2197</v>
-      </c>
-      <c r="G155" s="23" t="s">
-        <v>2198</v>
-      </c>
-      <c r="H155" s="6" t="s">
-        <v>2199</v>
-      </c>
-      <c r="I155" s="23" t="s">
-        <v>2200</v>
-      </c>
-      <c r="J155" s="23" t="s">
-        <v>2201</v>
-      </c>
-      <c r="K155" s="23" t="s">
-        <v>2202</v>
-      </c>
-      <c r="L155" s="23" t="s">
-        <v>2203</v>
-      </c>
-      <c r="M155" s="6" t="s">
-        <v>2204</v>
-      </c>
-      <c r="N155" s="6" t="s">
-        <v>2205</v>
-      </c>
-      <c r="O155" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="P155" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q155" s="10"/>
-      <c r="R155" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="S155" s="5"/>
-      <c r="T155" s="5"/>
-      <c r="U155" s="5"/>
-      <c r="V155" s="5"/>
-      <c r="W155" s="5"/>
-      <c r="X155" s="5"/>
-      <c r="Y155" s="5"/>
+      <c r="O155" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="P155" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q155" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="R155" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="S155" s="25"/>
+      <c r="T155" s="25"/>
+      <c r="U155" s="25"/>
+      <c r="V155" s="25"/>
+      <c r="W155" s="25"/>
+      <c r="X155" s="25"/>
+      <c r="Y155" s="25"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="11" t="s">
+      <c r="A156" s="5" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E156" s="23" t="s">
+        <v>2200</v>
+      </c>
+      <c r="F156" s="23" t="s">
+        <v>2201</v>
+      </c>
+      <c r="G156" s="23" t="s">
+        <v>2202</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>2203</v>
+      </c>
+      <c r="I156" s="23" t="s">
+        <v>2204</v>
+      </c>
+      <c r="J156" s="23" t="s">
+        <v>2205</v>
+      </c>
+      <c r="K156" s="23" t="s">
         <v>2206</v>
       </c>
-      <c r="B156" s="12" t="s">
+      <c r="L156" s="23" t="s">
         <v>2207</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="M156" s="6" t="s">
         <v>2208</v>
       </c>
-      <c r="D156" s="13" t="s">
+      <c r="N156" s="6" t="s">
         <v>2209</v>
       </c>
-      <c r="E156" s="12" t="s">
-        <v>1995</v>
-      </c>
-      <c r="F156" s="12" t="s">
-        <v>2210</v>
-      </c>
-      <c r="G156" s="12" t="s">
-        <v>2211</v>
-      </c>
-      <c r="H156" s="12" t="s">
-        <v>2212</v>
-      </c>
-      <c r="I156" s="12" t="s">
-        <v>2213</v>
-      </c>
-      <c r="J156" s="12" t="s">
-        <v>2214</v>
-      </c>
-      <c r="K156" s="12" t="s">
-        <v>2215</v>
-      </c>
-      <c r="L156" s="12" t="s">
-        <v>2216</v>
-      </c>
-      <c r="M156" s="12" t="s">
-        <v>2217</v>
-      </c>
-      <c r="N156" s="12" t="s">
-        <v>2218</v>
-      </c>
-      <c r="O156" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P156" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q156" s="15"/>
-      <c r="R156" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="S156" s="32" t="s">
-        <v>2219</v>
-      </c>
-      <c r="T156" s="11"/>
-      <c r="U156" s="11"/>
-      <c r="V156" s="11"/>
-      <c r="W156" s="11"/>
-      <c r="X156" s="11"/>
-      <c r="Y156" s="11"/>
+      <c r="O156" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P156" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q156" s="10"/>
+      <c r="R156" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S156" s="5"/>
+      <c r="T156" s="5"/>
+      <c r="U156" s="5"/>
+      <c r="V156" s="5"/>
+      <c r="W156" s="5"/>
+      <c r="X156" s="5"/>
+      <c r="Y156" s="5"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="25" t="s">
+      <c r="A157" s="11" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D157" s="13" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>1995</v>
+      </c>
+      <c r="F157" s="12" t="s">
+        <v>2214</v>
+      </c>
+      <c r="G157" s="12" t="s">
+        <v>2215</v>
+      </c>
+      <c r="H157" s="12" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I157" s="12" t="s">
+        <v>2217</v>
+      </c>
+      <c r="J157" s="12" t="s">
+        <v>2218</v>
+      </c>
+      <c r="K157" s="12" t="s">
+        <v>2219</v>
+      </c>
+      <c r="L157" s="12" t="s">
         <v>2220</v>
       </c>
-      <c r="B157" s="26" t="s">
+      <c r="M157" s="12" t="s">
         <v>2221</v>
       </c>
-      <c r="C157" s="26" t="s">
+      <c r="N157" s="12" t="s">
         <v>2222</v>
       </c>
-      <c r="D157" s="27" t="s">
+      <c r="O157" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P157" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q157" s="15"/>
+      <c r="R157" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="S157" s="32" t="s">
         <v>2223</v>
       </c>
-      <c r="E157" s="26" t="s">
-        <v>2224</v>
-      </c>
-      <c r="F157" s="26" t="s">
-        <v>2225</v>
-      </c>
-      <c r="G157" s="26" t="s">
-        <v>2226</v>
-      </c>
-      <c r="H157" s="26" t="s">
-        <v>2227</v>
-      </c>
-      <c r="I157" s="26" t="s">
-        <v>2228</v>
-      </c>
-      <c r="J157" s="26" t="s">
-        <v>2229</v>
-      </c>
-      <c r="K157" s="26" t="s">
-        <v>2230</v>
-      </c>
-      <c r="L157" s="26" t="s">
-        <v>2231</v>
-      </c>
-      <c r="M157" s="26" t="s">
-        <v>2232</v>
-      </c>
-      <c r="N157" s="26" t="s">
-        <v>2233</v>
-      </c>
-      <c r="O157" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="P157" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q157" s="29"/>
-      <c r="R157" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="S157" s="25"/>
-      <c r="T157" s="25"/>
-      <c r="U157" s="25"/>
-      <c r="V157" s="25"/>
-      <c r="W157" s="25"/>
-      <c r="X157" s="25"/>
-      <c r="Y157" s="25"/>
+      <c r="T157" s="11"/>
+      <c r="U157" s="11"/>
+      <c r="V157" s="11"/>
+      <c r="W157" s="11"/>
+      <c r="X157" s="11"/>
+      <c r="Y157" s="11"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="5" t="s">
+      <c r="A158" s="25" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B158" s="26" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C158" s="26" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D158" s="27" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E158" s="26" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F158" s="26" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G158" s="26" t="s">
+        <v>2230</v>
+      </c>
+      <c r="H158" s="26" t="s">
+        <v>2231</v>
+      </c>
+      <c r="I158" s="26" t="s">
+        <v>2232</v>
+      </c>
+      <c r="J158" s="26" t="s">
+        <v>2233</v>
+      </c>
+      <c r="K158" s="26" t="s">
         <v>2234</v>
       </c>
-      <c r="B158" s="6" t="s">
+      <c r="L158" s="26" t="s">
         <v>2235</v>
       </c>
-      <c r="C158" s="6" t="s">
+      <c r="M158" s="26" t="s">
         <v>2236</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="N158" s="26" t="s">
         <v>2237</v>
       </c>
-      <c r="E158" s="23" t="s">
-        <v>2238</v>
-      </c>
-      <c r="F158" s="23" t="s">
-        <v>2239</v>
-      </c>
-      <c r="G158" s="23" t="s">
-        <v>2240</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>2241</v>
-      </c>
-      <c r="I158" s="23" t="s">
-        <v>2242</v>
-      </c>
-      <c r="J158" s="23" t="s">
-        <v>2243</v>
-      </c>
-      <c r="K158" s="23" t="s">
-        <v>2244</v>
-      </c>
-      <c r="L158" s="23" t="s">
-        <v>2245</v>
-      </c>
-      <c r="M158" s="6" t="s">
-        <v>2246</v>
-      </c>
-      <c r="N158" s="6" t="s">
-        <v>2247</v>
-      </c>
-      <c r="O158" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="P158" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q158" s="10"/>
-      <c r="R158" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="S158" s="5"/>
-      <c r="T158" s="5"/>
-      <c r="U158" s="5"/>
-      <c r="V158" s="5"/>
-      <c r="W158" s="5"/>
-      <c r="X158" s="5"/>
-      <c r="Y158" s="5"/>
+      <c r="O158" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="P158" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q158" s="29"/>
+      <c r="R158" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="S158" s="25"/>
+      <c r="T158" s="25"/>
+      <c r="U158" s="25"/>
+      <c r="V158" s="25"/>
+      <c r="W158" s="25"/>
+      <c r="X158" s="25"/>
+      <c r="Y158" s="25"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="5" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>2241</v>
+      </c>
+      <c r="E159" s="23" t="s">
+        <v>2242</v>
+      </c>
+      <c r="F159" s="23" t="s">
+        <v>2243</v>
+      </c>
+      <c r="G159" s="23" t="s">
+        <v>2244</v>
+      </c>
+      <c r="H159" s="6" t="s">
+        <v>2245</v>
+      </c>
+      <c r="I159" s="23" t="s">
+        <v>2246</v>
+      </c>
+      <c r="J159" s="23" t="s">
+        <v>2247</v>
+      </c>
+      <c r="K159" s="23" t="s">
         <v>2248</v>
       </c>
-      <c r="B159" s="12" t="s">
+      <c r="L159" s="23" t="s">
         <v>2249</v>
       </c>
-      <c r="C159" s="12" t="s">
+      <c r="M159" s="6" t="s">
         <v>2250</v>
       </c>
-      <c r="D159" s="13" t="s">
+      <c r="N159" s="6" t="s">
         <v>2251</v>
       </c>
-      <c r="E159" s="12" t="s">
-        <v>2252</v>
-      </c>
-      <c r="F159" s="12" t="s">
-        <v>2253</v>
-      </c>
-      <c r="G159" s="12" t="s">
-        <v>2254</v>
-      </c>
-      <c r="H159" s="12" t="s">
-        <v>2255</v>
-      </c>
-      <c r="I159" s="12" t="s">
-        <v>2256</v>
-      </c>
-      <c r="J159" s="12" t="s">
-        <v>2257</v>
-      </c>
-      <c r="K159" s="12" t="s">
-        <v>2258</v>
-      </c>
-      <c r="L159" s="12" t="s">
-        <v>2259</v>
-      </c>
-      <c r="M159" s="12" t="s">
-        <v>2260</v>
-      </c>
-      <c r="N159" s="12" t="s">
-        <v>2261</v>
-      </c>
-      <c r="O159" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P159" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q159" s="15"/>
-      <c r="R159" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="S159" s="32" t="s">
-        <v>2262</v>
-      </c>
-      <c r="T159" s="11"/>
-      <c r="U159" s="11"/>
-      <c r="V159" s="11"/>
-      <c r="W159" s="11"/>
-      <c r="X159" s="11"/>
-      <c r="Y159" s="11"/>
+      <c r="O159" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P159" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q159" s="10"/>
+      <c r="R159" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S159" s="5"/>
+      <c r="T159" s="5"/>
+      <c r="U159" s="5"/>
+      <c r="V159" s="5"/>
+      <c r="W159" s="5"/>
+      <c r="X159" s="5"/>
+      <c r="Y159" s="5"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="16" t="s">
+      <c r="A160" s="11" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D160" s="13" t="s">
+        <v>2255</v>
+      </c>
+      <c r="E160" s="12" t="s">
+        <v>2256</v>
+      </c>
+      <c r="F160" s="12" t="s">
+        <v>2257</v>
+      </c>
+      <c r="G160" s="12" t="s">
+        <v>2258</v>
+      </c>
+      <c r="H160" s="12" t="s">
+        <v>2259</v>
+      </c>
+      <c r="I160" s="12" t="s">
+        <v>2260</v>
+      </c>
+      <c r="J160" s="12" t="s">
+        <v>2261</v>
+      </c>
+      <c r="K160" s="12" t="s">
+        <v>2262</v>
+      </c>
+      <c r="L160" s="12" t="s">
         <v>2263</v>
       </c>
-      <c r="B160" s="17" t="s">
+      <c r="M160" s="12" t="s">
         <v>2264</v>
       </c>
-      <c r="C160" s="17" t="s">
+      <c r="N160" s="12" t="s">
         <v>2265</v>
       </c>
-      <c r="D160" s="18" t="s">
+      <c r="O160" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P160" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q160" s="15"/>
+      <c r="R160" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="S160" s="32" t="s">
         <v>2266</v>
       </c>
-      <c r="E160" s="17" t="s">
+      <c r="T160" s="11"/>
+      <c r="U160" s="11"/>
+      <c r="V160" s="11"/>
+      <c r="W160" s="11"/>
+      <c r="X160" s="11"/>
+      <c r="Y160" s="11"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="16" t="s">
         <v>2267</v>
       </c>
-      <c r="F160" s="17" t="s">
+      <c r="B161" s="17" t="s">
         <v>2268</v>
       </c>
-      <c r="G160" s="17" t="s">
+      <c r="C161" s="17" t="s">
         <v>2269</v>
       </c>
-      <c r="H160" s="17" t="s">
+      <c r="D161" s="18" t="s">
         <v>2270</v>
       </c>
-      <c r="I160" s="17" t="s">
+      <c r="E161" s="17" t="s">
         <v>2271</v>
       </c>
-      <c r="J160" s="17" t="s">
+      <c r="F161" s="17" t="s">
         <v>2272</v>
       </c>
-      <c r="K160" s="17" t="s">
+      <c r="G161" s="17" t="s">
         <v>2273</v>
       </c>
-      <c r="L160" s="17" t="s">
+      <c r="H161" s="17" t="s">
         <v>2274</v>
       </c>
-      <c r="M160" s="17" t="s">
+      <c r="I161" s="17" t="s">
         <v>2275</v>
       </c>
-      <c r="N160" s="17" t="s">
+      <c r="J161" s="17" t="s">
         <v>2276</v>
       </c>
-      <c r="O160" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="P160" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q160" s="21"/>
-      <c r="R160" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="S160" s="16"/>
-      <c r="T160" s="16"/>
-      <c r="U160" s="16"/>
-      <c r="V160" s="16"/>
-      <c r="W160" s="16"/>
-      <c r="X160" s="16"/>
-      <c r="Y160" s="16"/>
+      <c r="K161" s="17" t="s">
+        <v>2277</v>
+      </c>
+      <c r="L161" s="17" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M161" s="17" t="s">
+        <v>2279</v>
+      </c>
+      <c r="N161" s="17" t="s">
+        <v>2280</v>
+      </c>
+      <c r="O161" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="P161" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q161" s="21"/>
+      <c r="R161" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="S161" s="16"/>
+      <c r="T161" s="16"/>
+      <c r="U161" s="16"/>
+      <c r="V161" s="16"/>
+      <c r="W161" s="16"/>
+      <c r="X161" s="16"/>
+      <c r="Y161" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$Y$160"/>
+  <autoFilter ref="$A$1:$Y$161"/>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:R27 Q28:R28 P29:R160">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:R27 Q28:R28 P29:R151 Q152 P153:R161">
       <formula1>"Include,Exclude"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O27 O28:P28 O29:O160">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O27 O28:P28 O29:O151 O152:P152 R152 O153:O161">
       <formula1>"Exclude,Include"</formula1>
     </dataValidation>
   </dataValidations>
@@ -25663,10 +25732,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>2278</v>
+        <v>2282</v>
       </c>
       <c r="C1" s="46"/>
       <c r="D1" s="47"/>
@@ -25697,10 +25766,10 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>2279</v>
+        <v>2283</v>
       </c>
       <c r="C2" s="46"/>
       <c r="D2" s="47"/>
@@ -25731,10 +25800,10 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>2280</v>
+        <v>2284</v>
       </c>
       <c r="C3" s="46"/>
       <c r="D3" s="47"/>
@@ -25765,10 +25834,10 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>2281</v>
+        <v>2285</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="47"/>
@@ -25799,10 +25868,10 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>2282</v>
+        <v>2286</v>
       </c>
       <c r="C5" s="46"/>
       <c r="D5" s="47"/>
@@ -25833,10 +25902,10 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>2283</v>
+        <v>2287</v>
       </c>
       <c r="C6" s="46"/>
       <c r="D6" s="47"/>
@@ -25867,10 +25936,10 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>2284</v>
+        <v>2288</v>
       </c>
       <c r="C7" s="46"/>
       <c r="D7" s="47"/>
@@ -25901,10 +25970,10 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>2285</v>
+        <v>2289</v>
       </c>
       <c r="C8" s="46"/>
       <c r="D8" s="47"/>
@@ -25935,10 +26004,10 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>2286</v>
+        <v>2290</v>
       </c>
       <c r="C9" s="46"/>
       <c r="D9" s="47"/>
@@ -25969,10 +26038,10 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>2287</v>
+        <v>2291</v>
       </c>
       <c r="C10" s="46"/>
       <c r="D10" s="47"/>
@@ -26003,10 +26072,10 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>2288</v>
+        <v>2292</v>
       </c>
       <c r="C11" s="46"/>
       <c r="D11" s="47"/>
@@ -26037,10 +26106,10 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>2289</v>
+        <v>2293</v>
       </c>
       <c r="C12" s="46"/>
       <c r="D12" s="47"/>
@@ -26071,10 +26140,10 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>2290</v>
+        <v>2294</v>
       </c>
       <c r="C13" s="46"/>
       <c r="D13" s="47"/>
@@ -26105,10 +26174,10 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>2291</v>
+        <v>2295</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="47"/>
@@ -26139,10 +26208,10 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>2292</v>
+        <v>2296</v>
       </c>
       <c r="C15" s="46"/>
       <c r="D15" s="48"/>
@@ -26173,10 +26242,10 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>2293</v>
+        <v>2297</v>
       </c>
       <c r="C16" s="46"/>
       <c r="D16" s="48"/>
@@ -26207,10 +26276,10 @@
     </row>
     <row r="17">
       <c r="A17" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>2294</v>
+        <v>2298</v>
       </c>
       <c r="C17" s="46"/>
       <c r="D17" s="47"/>
@@ -26241,10 +26310,10 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>2295</v>
+        <v>2299</v>
       </c>
       <c r="C18" s="46"/>
       <c r="D18" s="47"/>
@@ -26275,10 +26344,10 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>2296</v>
+        <v>2300</v>
       </c>
       <c r="C19" s="46"/>
       <c r="D19" s="47"/>
@@ -26309,10 +26378,10 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>2297</v>
+        <v>2301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="47"/>
@@ -26343,10 +26412,10 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>2298</v>
+        <v>2302</v>
       </c>
       <c r="C21" s="46"/>
       <c r="D21" s="47"/>
@@ -26377,10 +26446,10 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>2299</v>
+        <v>2303</v>
       </c>
       <c r="C22" s="46"/>
       <c r="D22" s="47"/>
@@ -26411,10 +26480,10 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>2300</v>
+        <v>2304</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="47"/>
@@ -26445,10 +26514,10 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>2301</v>
+        <v>2305</v>
       </c>
       <c r="C24" s="46"/>
       <c r="D24" s="47"/>
@@ -26479,10 +26548,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>2302</v>
+        <v>2306</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="47"/>
@@ -26513,10 +26582,10 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>2303</v>
+        <v>2307</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="47"/>
@@ -26547,10 +26616,10 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>2304</v>
+        <v>2308</v>
       </c>
       <c r="C27" s="46"/>
       <c r="D27" s="47"/>
@@ -26581,10 +26650,10 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>2305</v>
+        <v>2309</v>
       </c>
       <c r="C28" s="46"/>
       <c r="D28" s="47"/>
@@ -26615,10 +26684,10 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>2306</v>
+        <v>2310</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="47"/>
@@ -26649,10 +26718,10 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>2307</v>
+        <v>2311</v>
       </c>
       <c r="C30" s="46"/>
       <c r="D30" s="47"/>
@@ -26683,10 +26752,10 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>2308</v>
+        <v>2312</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="47"/>
@@ -26717,10 +26786,10 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>2309</v>
+        <v>2313</v>
       </c>
       <c r="C32" s="46"/>
       <c r="D32" s="47"/>
@@ -26751,10 +26820,10 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B33" s="45" t="s">
-        <v>2310</v>
+        <v>2314</v>
       </c>
       <c r="C33" s="46"/>
       <c r="D33" s="47"/>
@@ -26785,10 +26854,10 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>2311</v>
+        <v>2315</v>
       </c>
       <c r="C34" s="46"/>
       <c r="D34" s="47"/>
@@ -26819,10 +26888,10 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>2312</v>
+        <v>2316</v>
       </c>
       <c r="C35" s="46"/>
       <c r="D35" s="47"/>
@@ -26853,10 +26922,10 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>2313</v>
+        <v>2317</v>
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="47"/>
@@ -26887,10 +26956,10 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="44" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>2314</v>
+        <v>2318</v>
       </c>
       <c r="C37" s="46"/>
       <c r="D37" s="47"/>
@@ -26951,7 +27020,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="50" t="s">
-        <v>2315</v>
+        <v>2319</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -26996,7 +27065,7 @@
         <v>13</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>2316</v>
+        <v>2320</v>
       </c>
       <c r="Q1" s="38"/>
       <c r="R1" s="38"/>
@@ -27005,49 +27074,49 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>2317</v>
+        <v>2321</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>2318</v>
+        <v>2322</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>2319</v>
+        <v>2323</v>
       </c>
       <c r="E2" s="54" t="s">
-        <v>2320</v>
+        <v>2324</v>
       </c>
       <c r="F2" s="53" t="s">
-        <v>2321</v>
+        <v>2325</v>
       </c>
       <c r="G2" s="53" t="s">
-        <v>2322</v>
+        <v>2326</v>
       </c>
       <c r="H2" s="53" t="s">
-        <v>2323</v>
+        <v>2327</v>
       </c>
       <c r="I2" s="53" t="s">
-        <v>2324</v>
+        <v>2328</v>
       </c>
       <c r="J2" s="53" t="s">
-        <v>2325</v>
+        <v>2329</v>
       </c>
       <c r="K2" s="53" t="s">
-        <v>2326</v>
+        <v>2330</v>
       </c>
       <c r="L2" s="53" t="s">
-        <v>2327</v>
+        <v>2331</v>
       </c>
       <c r="M2" s="53" t="s">
-        <v>2328</v>
+        <v>2332</v>
       </c>
       <c r="N2" s="53" t="s">
-        <v>2329</v>
+        <v>2333</v>
       </c>
       <c r="O2" s="53" t="s">
-        <v>2330</v>
+        <v>2334</v>
       </c>
       <c r="P2" s="54"/>
       <c r="Q2" s="55"/>
@@ -27064,49 +27133,49 @@
     </row>
     <row r="3">
       <c r="A3" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>2331</v>
+        <v>2335</v>
       </c>
       <c r="C3" s="53" t="s">
-        <v>2332</v>
+        <v>2336</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>2333</v>
+        <v>2337</v>
       </c>
       <c r="E3" s="54" t="s">
-        <v>2334</v>
+        <v>2338</v>
       </c>
       <c r="F3" s="53" t="s">
-        <v>2335</v>
+        <v>2339</v>
       </c>
       <c r="G3" s="53" t="s">
-        <v>2336</v>
+        <v>2340</v>
       </c>
       <c r="H3" s="53" t="s">
-        <v>2337</v>
+        <v>2341</v>
       </c>
       <c r="I3" s="53" t="s">
-        <v>2338</v>
+        <v>2342</v>
       </c>
       <c r="J3" s="53" t="s">
-        <v>2339</v>
+        <v>2343</v>
       </c>
       <c r="K3" s="53" t="s">
-        <v>2340</v>
+        <v>2344</v>
       </c>
       <c r="L3" s="53" t="s">
-        <v>2341</v>
+        <v>2345</v>
       </c>
       <c r="M3" s="53" t="s">
-        <v>2342</v>
+        <v>2346</v>
       </c>
       <c r="N3" s="53" t="s">
-        <v>2343</v>
+        <v>2347</v>
       </c>
       <c r="O3" s="53" t="s">
-        <v>2344</v>
+        <v>2348</v>
       </c>
       <c r="P3" s="54"/>
       <c r="Q3" s="55"/>
@@ -27123,49 +27192,49 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>2345</v>
+        <v>2349</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>2346</v>
+        <v>2350</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>2347</v>
+        <v>2351</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>2348</v>
+        <v>2352</v>
       </c>
       <c r="F4" s="53" t="s">
-        <v>2349</v>
+        <v>2353</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>2350</v>
+        <v>2354</v>
       </c>
       <c r="H4" s="53" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="I4" s="53" t="s">
-        <v>2352</v>
+        <v>2356</v>
       </c>
       <c r="J4" s="53" t="s">
-        <v>2353</v>
+        <v>2357</v>
       </c>
       <c r="K4" s="53" t="s">
-        <v>2354</v>
+        <v>2358</v>
       </c>
       <c r="L4" s="53" t="s">
-        <v>2355</v>
+        <v>2359</v>
       </c>
       <c r="M4" s="53" t="s">
-        <v>2356</v>
+        <v>2360</v>
       </c>
       <c r="N4" s="53" t="s">
-        <v>2357</v>
+        <v>2361</v>
       </c>
       <c r="O4" s="53" t="s">
-        <v>2358</v>
+        <v>2362</v>
       </c>
       <c r="P4" s="54"/>
       <c r="Q4" s="55"/>
@@ -27182,49 +27251,49 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>2359</v>
+        <v>2363</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>2360</v>
+        <v>2364</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>2361</v>
+        <v>2365</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>2362</v>
+        <v>2366</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>2363</v>
+        <v>2367</v>
       </c>
       <c r="G5" s="53" t="s">
-        <v>2364</v>
+        <v>2368</v>
       </c>
       <c r="H5" s="53" t="s">
-        <v>2365</v>
+        <v>2369</v>
       </c>
       <c r="I5" s="53" t="s">
-        <v>2366</v>
+        <v>2370</v>
       </c>
       <c r="J5" s="53" t="s">
-        <v>2367</v>
+        <v>2371</v>
       </c>
       <c r="K5" s="53" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="L5" s="53" t="s">
-        <v>2369</v>
+        <v>2373</v>
       </c>
       <c r="M5" s="53" t="s">
-        <v>2370</v>
+        <v>2374</v>
       </c>
       <c r="N5" s="53" t="s">
-        <v>2371</v>
+        <v>2375</v>
       </c>
       <c r="O5" s="53" t="s">
-        <v>2372</v>
+        <v>2376</v>
       </c>
       <c r="P5" s="54"/>
       <c r="Q5" s="55"/>
@@ -27241,49 +27310,49 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>2373</v>
+        <v>2377</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>2374</v>
+        <v>2378</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>2375</v>
+        <v>2379</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>2376</v>
+        <v>2380</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>2377</v>
+        <v>2381</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>2378</v>
+        <v>2382</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>2379</v>
+        <v>2383</v>
       </c>
       <c r="I6" s="53" t="s">
-        <v>2380</v>
+        <v>2384</v>
       </c>
       <c r="J6" s="53" t="s">
-        <v>2381</v>
+        <v>2385</v>
       </c>
       <c r="K6" s="53" t="s">
-        <v>2382</v>
+        <v>2386</v>
       </c>
       <c r="L6" s="53" t="s">
-        <v>2383</v>
+        <v>2387</v>
       </c>
       <c r="M6" s="53" t="s">
-        <v>2384</v>
+        <v>2388</v>
       </c>
       <c r="N6" s="53" t="s">
-        <v>2385</v>
+        <v>2389</v>
       </c>
       <c r="O6" s="53" t="s">
-        <v>2386</v>
+        <v>2390</v>
       </c>
       <c r="P6" s="54"/>
       <c r="Q6" s="55"/>
@@ -27300,49 +27369,49 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>2387</v>
+        <v>2391</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>2388</v>
+        <v>2392</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>2389</v>
+        <v>2393</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>2390</v>
+        <v>2394</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>2391</v>
+        <v>2395</v>
       </c>
       <c r="G7" s="53" t="s">
-        <v>2392</v>
+        <v>2396</v>
       </c>
       <c r="H7" s="53" t="s">
-        <v>2393</v>
+        <v>2397</v>
       </c>
       <c r="I7" s="53" t="s">
-        <v>2394</v>
+        <v>2398</v>
       </c>
       <c r="J7" s="53" t="s">
-        <v>2395</v>
+        <v>2399</v>
       </c>
       <c r="K7" s="53" t="s">
-        <v>2396</v>
+        <v>2400</v>
       </c>
       <c r="L7" s="53" t="s">
-        <v>2397</v>
+        <v>2401</v>
       </c>
       <c r="M7" s="53" t="s">
-        <v>2398</v>
+        <v>2402</v>
       </c>
       <c r="N7" s="53" t="s">
-        <v>2399</v>
+        <v>2403</v>
       </c>
       <c r="O7" s="53" t="s">
-        <v>2400</v>
+        <v>2404</v>
       </c>
       <c r="P7" s="54"/>
       <c r="Q7" s="55"/>
@@ -27359,49 +27428,49 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>2401</v>
+        <v>2405</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>2402</v>
+        <v>2406</v>
       </c>
       <c r="D8" s="53" t="s">
-        <v>2403</v>
+        <v>2407</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>2404</v>
+        <v>2408</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>2405</v>
+        <v>2409</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>2406</v>
+        <v>2410</v>
       </c>
       <c r="H8" s="53" t="s">
-        <v>2407</v>
+        <v>2411</v>
       </c>
       <c r="I8" s="53" t="s">
-        <v>2408</v>
+        <v>2412</v>
       </c>
       <c r="J8" s="53" t="s">
-        <v>2409</v>
+        <v>2413</v>
       </c>
       <c r="K8" s="53" t="s">
-        <v>2410</v>
+        <v>2414</v>
       </c>
       <c r="L8" s="53" t="s">
-        <v>2411</v>
+        <v>2415</v>
       </c>
       <c r="M8" s="53" t="s">
-        <v>2412</v>
+        <v>2416</v>
       </c>
       <c r="N8" s="53" t="s">
-        <v>2413</v>
+        <v>2417</v>
       </c>
       <c r="O8" s="53" t="s">
-        <v>2414</v>
+        <v>2418</v>
       </c>
       <c r="P8" s="54"/>
       <c r="Q8" s="55"/>
@@ -27418,49 +27487,49 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>2415</v>
+        <v>2419</v>
       </c>
       <c r="C9" s="53" t="s">
-        <v>2416</v>
+        <v>2420</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>2417</v>
+        <v>2421</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>2418</v>
+        <v>2422</v>
       </c>
       <c r="F9" s="53" t="s">
-        <v>2419</v>
+        <v>2423</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>2420</v>
+        <v>2424</v>
       </c>
       <c r="H9" s="53" t="s">
-        <v>2421</v>
+        <v>2425</v>
       </c>
       <c r="I9" s="53" t="s">
-        <v>2422</v>
+        <v>2426</v>
       </c>
       <c r="J9" s="53" t="s">
-        <v>2423</v>
+        <v>2427</v>
       </c>
       <c r="K9" s="53" t="s">
-        <v>2424</v>
+        <v>2428</v>
       </c>
       <c r="L9" s="53" t="s">
-        <v>2425</v>
+        <v>2429</v>
       </c>
       <c r="M9" s="53" t="s">
-        <v>2426</v>
+        <v>2430</v>
       </c>
       <c r="N9" s="53" t="s">
-        <v>2427</v>
+        <v>2431</v>
       </c>
       <c r="O9" s="53" t="s">
-        <v>2428</v>
+        <v>2432</v>
       </c>
       <c r="P9" s="54"/>
       <c r="Q9" s="55"/>
@@ -27477,49 +27546,49 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>2429</v>
+        <v>2433</v>
       </c>
       <c r="C10" s="53" t="s">
         <v>1749</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>2430</v>
+        <v>2434</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>2431</v>
+        <v>2435</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>2432</v>
+        <v>2436</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>2433</v>
+        <v>2437</v>
       </c>
       <c r="H10" s="53" t="s">
-        <v>2434</v>
+        <v>2438</v>
       </c>
       <c r="I10" s="53" t="s">
-        <v>2435</v>
+        <v>2439</v>
       </c>
       <c r="J10" s="53" t="s">
-        <v>2436</v>
+        <v>2440</v>
       </c>
       <c r="K10" s="53" t="s">
-        <v>2437</v>
+        <v>2441</v>
       </c>
       <c r="L10" s="53" t="s">
-        <v>2438</v>
+        <v>2442</v>
       </c>
       <c r="M10" s="53" t="s">
-        <v>2439</v>
+        <v>2443</v>
       </c>
       <c r="N10" s="53" t="s">
-        <v>2440</v>
+        <v>2444</v>
       </c>
       <c r="O10" s="53" t="s">
-        <v>2441</v>
+        <v>2445</v>
       </c>
       <c r="P10" s="54"/>
       <c r="Q10" s="55"/>
@@ -27536,49 +27605,49 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>2442</v>
+        <v>2446</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>2443</v>
+        <v>2447</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>2444</v>
+        <v>2448</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>2445</v>
+        <v>2449</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>2446</v>
+        <v>2450</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>2447</v>
+        <v>2451</v>
       </c>
       <c r="H11" s="53" t="s">
-        <v>2448</v>
+        <v>2452</v>
       </c>
       <c r="I11" s="53" t="s">
-        <v>2449</v>
+        <v>2453</v>
       </c>
       <c r="J11" s="53" t="s">
-        <v>2450</v>
+        <v>2454</v>
       </c>
       <c r="K11" s="53" t="s">
-        <v>2451</v>
+        <v>2455</v>
       </c>
       <c r="L11" s="53" t="s">
-        <v>2452</v>
+        <v>2456</v>
       </c>
       <c r="M11" s="53" t="s">
-        <v>2453</v>
+        <v>2457</v>
       </c>
       <c r="N11" s="53" t="s">
-        <v>2454</v>
+        <v>2458</v>
       </c>
       <c r="O11" s="53" t="s">
-        <v>2455</v>
+        <v>2459</v>
       </c>
       <c r="P11" s="54"/>
       <c r="Q11" s="55"/>
@@ -27595,49 +27664,49 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>2456</v>
+        <v>2460</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>2457</v>
+        <v>2461</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>2458</v>
+        <v>2462</v>
       </c>
       <c r="E12" s="54" t="s">
-        <v>2459</v>
+        <v>2463</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>2460</v>
+        <v>2464</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>2461</v>
+        <v>2465</v>
       </c>
       <c r="H12" s="53" t="s">
-        <v>2462</v>
+        <v>2466</v>
       </c>
       <c r="I12" s="53" t="s">
-        <v>2463</v>
+        <v>2467</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>2464</v>
+        <v>2468</v>
       </c>
       <c r="K12" s="53" t="s">
-        <v>2465</v>
+        <v>2469</v>
       </c>
       <c r="L12" s="53" t="s">
-        <v>2466</v>
+        <v>2470</v>
       </c>
       <c r="M12" s="53" t="s">
-        <v>2467</v>
+        <v>2471</v>
       </c>
       <c r="N12" s="53" t="s">
-        <v>2468</v>
+        <v>2472</v>
       </c>
       <c r="O12" s="53" t="s">
-        <v>2469</v>
+        <v>2473</v>
       </c>
       <c r="P12" s="54"/>
       <c r="Q12" s="55"/>
@@ -27654,49 +27723,49 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>2470</v>
+        <v>2474</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>2471</v>
+        <v>2475</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>2472</v>
+        <v>2476</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>2473</v>
+        <v>2477</v>
       </c>
       <c r="F13" s="56" t="s">
-        <v>2474</v>
+        <v>2478</v>
       </c>
       <c r="G13" s="52" t="s">
-        <v>2475</v>
+        <v>2479</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>2476</v>
+        <v>2480</v>
       </c>
       <c r="I13" s="52" t="s">
-        <v>2477</v>
+        <v>2481</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>2478</v>
+        <v>2482</v>
       </c>
       <c r="K13" s="52" t="s">
-        <v>2479</v>
+        <v>2483</v>
       </c>
       <c r="L13" s="52" t="s">
-        <v>2480</v>
+        <v>2484</v>
       </c>
       <c r="M13" s="52" t="s">
-        <v>2481</v>
+        <v>2485</v>
       </c>
       <c r="N13" s="52" t="s">
-        <v>2482</v>
+        <v>2486</v>
       </c>
       <c r="O13" s="52" t="s">
-        <v>2483</v>
+        <v>2487</v>
       </c>
       <c r="P13" s="54"/>
       <c r="Q13" s="55"/>
@@ -27713,49 +27782,49 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>2484</v>
+        <v>2488</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>2485</v>
+        <v>2489</v>
       </c>
       <c r="D14" s="53" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="E14" s="54" t="s">
-        <v>2487</v>
+        <v>2491</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>2488</v>
+        <v>2492</v>
       </c>
       <c r="G14" s="53" t="s">
-        <v>2489</v>
+        <v>2493</v>
       </c>
       <c r="H14" s="53" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
       <c r="I14" s="53" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="K14" s="53" t="s">
-        <v>2493</v>
+        <v>2497</v>
       </c>
       <c r="L14" s="53" t="s">
-        <v>2494</v>
+        <v>2498</v>
       </c>
       <c r="M14" s="53" t="s">
-        <v>2495</v>
+        <v>2499</v>
       </c>
       <c r="N14" s="53" t="s">
-        <v>2496</v>
+        <v>2500</v>
       </c>
       <c r="O14" s="53" t="s">
-        <v>2497</v>
+        <v>2501</v>
       </c>
       <c r="P14" s="54"/>
       <c r="Q14" s="55"/>
@@ -27772,49 +27841,49 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="51" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>2498</v>
+        <v>2502</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>2499</v>
+        <v>2503</v>
       </c>
       <c r="D15" s="53" t="s">
-        <v>2500</v>
+        <v>2504</v>
       </c>
       <c r="E15" s="54" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="F15" s="53" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="G15" s="53" t="s">
-        <v>2503</v>
+        <v>2507</v>
       </c>
       <c r="H15" s="53" t="s">
-        <v>2504</v>
+        <v>2508</v>
       </c>
       <c r="I15" s="53" t="s">
-        <v>2505</v>
+        <v>2509</v>
       </c>
       <c r="J15" s="53" t="s">
-        <v>2506</v>
+        <v>2510</v>
       </c>
       <c r="K15" s="53" t="s">
-        <v>2507</v>
+        <v>2511</v>
       </c>
       <c r="L15" s="53" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="M15" s="53" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="N15" s="53" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
       <c r="O15" s="53" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="P15" s="54"/>
       <c r="Q15" s="55"/>
